--- a/data/trans_camb/P19C03-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P19C03-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,06; -3,59</t>
+          <t>-15,25; -3,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,81; -0,57</t>
+          <t>-12,57; -1,04</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,33; -7,65</t>
+          <t>-19,23; -7,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,87; -3,33</t>
+          <t>-13,95; -3,14</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-14,95; -4,38</t>
+          <t>-15,08; -4,51</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,73; -13,1</t>
+          <t>-22,66; -12,95</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-13,04; -4,92</t>
+          <t>-13,06; -5,08</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,29; -4,4</t>
+          <t>-12,89; -4,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-19,27; -11,93</t>
+          <t>-19,32; -11,76</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-36,86; -10,54</t>
+          <t>-37,86; -8,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-32,57; -1,76</t>
+          <t>-31,58; -2,93</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-48,76; -22,08</t>
+          <t>-47,99; -22,04</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,34; -9,97</t>
+          <t>-36,64; -9,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,9; -13,72</t>
+          <t>-39,22; -13,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-58,95; -40,56</t>
+          <t>-58,52; -40,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,64; -14,37</t>
+          <t>-33,74; -14,69</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,25; -12,77</t>
+          <t>-33,49; -13,24</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-50,6; -34,51</t>
+          <t>-50,49; -34,32</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 6,94</t>
+          <t>-3,76; 6,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,12; 1,15</t>
+          <t>-8,47; 0,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-24,85; -11,5</t>
+          <t>-24,92; -11,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,03; 2,08</t>
+          <t>-7,18; 2,37</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-10,54; -1,82</t>
+          <t>-11,06; -1,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,08; -11,25</t>
+          <t>-19,57; -11,47</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 3,03</t>
+          <t>-3,72; 3,22</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,3; -1,92</t>
+          <t>-8,1; -1,85</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-22,22; -13,02</t>
+          <t>-22,13; -13,17</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,12; 24,87</t>
+          <t>-11,52; 24,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-25,43; 3,97</t>
+          <t>-26,24; 2,84</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-78,12; -40,99</t>
+          <t>-77,12; -39,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-19,96; 6,74</t>
+          <t>-20,34; 8,05</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-30,5; -6,21</t>
+          <t>-31,29; -5,19</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,27; -37,24</t>
+          <t>-54,84; -37,95</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,09; 10,05</t>
+          <t>-11,22; 10,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-25,14; -6,6</t>
+          <t>-24,78; -6,24</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-69,73; -43,43</t>
+          <t>-70,72; -43,13</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,46; 0,93</t>
+          <t>-11,07; 0,95</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,44; 3,63</t>
+          <t>-8,57; 3,91</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-16,64; -5,5</t>
+          <t>-17,27; -5,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,14; 3,22</t>
+          <t>-7,59; 3,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 5,02</t>
+          <t>-6,49; 4,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-23,72; -2,43</t>
+          <t>-24,25; -3,35</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,35; 0,25</t>
+          <t>-7,3; 0,5</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 2,75</t>
+          <t>-5,45; 2,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-20,21; -6,36</t>
+          <t>-20,38; -6,44</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-26,92; 2,91</t>
+          <t>-28,5; 2,82</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-21,74; 11,77</t>
+          <t>-22,33; 12,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-43,53; -16,99</t>
+          <t>-44,29; -15,53</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-20,65; 10,7</t>
+          <t>-21,35; 10,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-16,4; 16,53</t>
+          <t>-18,67; 15,72</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-69,91; -8,9</t>
+          <t>-71,95; -10,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-20,28; 0,79</t>
+          <t>-20,29; 1,63</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-14,72; 8,68</t>
+          <t>-15,0; 8,24</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-59,26; -19,65</t>
+          <t>-58,32; -20,48</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 5,84</t>
+          <t>-3,46; 5,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,07; 0,07</t>
+          <t>-9,23; 0,14</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,09; -7,66</t>
+          <t>-16,08; -7,95</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 3,71</t>
+          <t>-4,7; 3,97</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,21; -1,88</t>
+          <t>-10,32; -1,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-17,92; -9,78</t>
+          <t>-18,45; -10,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,58; 3,4</t>
+          <t>-2,97; 3,5</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,4; -2,32</t>
+          <t>-8,43; -2,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-15,86; -10,0</t>
+          <t>-15,8; -9,98</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,12; 22,84</t>
+          <t>-11,25; 23,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-30,08; 0,11</t>
+          <t>-30,16; 0,59</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-53,6; -29,57</t>
+          <t>-54,25; -30,91</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-14,83; 14,29</t>
+          <t>-15,22; 15,11</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,02; -6,68</t>
+          <t>-33,9; -7,01</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-59,65; -37,24</t>
+          <t>-59,7; -38,34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,78; 13,04</t>
+          <t>-10,0; 12,99</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-28,11; -8,72</t>
+          <t>-28,63; -8,86</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-53,6; -37,76</t>
+          <t>-53,29; -37,74</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 0,59</t>
+          <t>-4,59; 0,43</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,93; -1,73</t>
+          <t>-6,92; -1,84</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-18,39; -11,29</t>
+          <t>-18,41; -11,35</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,67; -0,84</t>
+          <t>-5,43; -0,57</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,03; -3,15</t>
+          <t>-8,11; -3,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-18,2; -11,53</t>
+          <t>-18,25; -11,76</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,39; -0,76</t>
+          <t>-4,53; -0,98</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-7,08; -3,45</t>
+          <t>-6,89; -3,27</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-16,97; -12,26</t>
+          <t>-16,68; -12,24</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-14,02; 1,98</t>
+          <t>-13,73; 1,46</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-21,12; -5,98</t>
+          <t>-20,69; -5,48</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-56,54; -36,05</t>
+          <t>-57,45; -36,86</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-17,08; -2,93</t>
+          <t>-16,3; -1,89</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-24,13; -10,36</t>
+          <t>-24,45; -10,59</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-55,51; -36,97</t>
+          <t>-55,08; -37,47</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-13,33; -2,36</t>
+          <t>-13,74; -3,14</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-21,32; -11,16</t>
+          <t>-20,87; -10,41</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-52,18; -38,94</t>
+          <t>-51,4; -39,13</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P19C03-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/P19C03-Habitat-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-13,61</t>
+          <t>-14,06</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-17,88</t>
+          <t>-17,74</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-15,79</t>
+          <t>-15,95</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-15,25; -3,0</t>
+          <t>-14,83; -2,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-12,57; -1,04</t>
+          <t>-13,51; -1,44</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-19,23; -7,54</t>
+          <t>-20,0; -8,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,95; -3,14</t>
+          <t>-14,16; -3,19</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-15,08; -4,51</t>
+          <t>-14,85; -4,07</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-22,66; -12,95</t>
+          <t>-22,53; -12,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-13,06; -5,08</t>
+          <t>-13,2; -5,27</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-12,89; -4,59</t>
+          <t>-12,55; -4,82</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-19,32; -11,76</t>
+          <t>-19,63; -12,41</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-36,7%</t>
+          <t>-37,93%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-49,98%</t>
+          <t>-49,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-43,4%</t>
+          <t>-43,82%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-37,86; -8,9</t>
+          <t>-36,71; -8,51</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-31,58; -2,93</t>
+          <t>-33,35; -4,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-47,99; -22,04</t>
+          <t>-49,95; -24,11</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-36,64; -9,73</t>
+          <t>-36,21; -9,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-39,22; -13,96</t>
+          <t>-39,42; -12,5</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-58,52; -40,71</t>
+          <t>-57,88; -39,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-33,74; -14,69</t>
+          <t>-34,08; -14,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-33,49; -13,24</t>
+          <t>-32,57; -13,9</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-50,49; -34,32</t>
+          <t>-51,22; -36,08</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-16,9</t>
+          <t>-13,39</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-15,27</t>
+          <t>-15,2</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-16,4</t>
+          <t>-14,36</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 6,68</t>
+          <t>-3,0; 7,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,47; 0,76</t>
+          <t>-8,63; 0,64</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-24,92; -11,11</t>
+          <t>-17,6; -9,09</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 2,37</t>
+          <t>-6,9; 2,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,06; -1,56</t>
+          <t>-10,68; -1,88</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,57; -11,47</t>
+          <t>-19,47; -11,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,72; 3,22</t>
+          <t>-3,77; 2,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-8,1; -1,85</t>
+          <t>-8,33; -1,38</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-22,13; -13,17</t>
+          <t>-17,11; -11,67</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-56,41%</t>
+          <t>-44,69%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-46,59%</t>
+          <t>-46,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-52,15%</t>
+          <t>-45,68%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 24,29</t>
+          <t>-9,22; 26,49</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-26,24; 2,84</t>
+          <t>-26,39; 2,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-77,12; -39,56</t>
+          <t>-53,84; -32,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 8,05</t>
+          <t>-19,55; 7,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-31,29; -5,19</t>
+          <t>-30,44; -5,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-54,84; -37,95</t>
+          <t>-54,57; -37,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-11,22; 10,93</t>
+          <t>-11,24; 8,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-24,78; -6,24</t>
+          <t>-24,98; -4,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-70,72; -43,13</t>
+          <t>-51,86; -38,99</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-11,2</t>
+          <t>-11,58</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-12,34</t>
+          <t>-9,81</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-12,02</t>
+          <t>-10,65</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,07; 0,95</t>
+          <t>-10,22; 1,16</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 3,91</t>
+          <t>-8,17; 4,15</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,27; -5,2</t>
+          <t>-17,12; -5,5</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-7,59; 3,21</t>
+          <t>-8,19; 2,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,49; 4,61</t>
+          <t>-6,39; 4,71</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-24,25; -3,35</t>
+          <t>-14,48; -5,16</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 0,5</t>
+          <t>-7,07; 0,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 2,65</t>
+          <t>-5,21; 2,53</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-20,38; -6,44</t>
+          <t>-14,35; -6,98</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-31,57%</t>
+          <t>-32,66%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-38,0%</t>
+          <t>-30,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-35,43%</t>
+          <t>-31,41%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-28,5; 2,82</t>
+          <t>-26,91; 4,08</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-22,33; 12,31</t>
+          <t>-21,86; 13,04</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-44,29; -15,53</t>
+          <t>-45,42; -18,48</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-21,35; 10,71</t>
+          <t>-22,64; 8,74</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-18,67; 15,72</t>
+          <t>-17,86; 15,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-71,95; -10,47</t>
+          <t>-41,48; -17,51</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-20,29; 1,63</t>
+          <t>-19,42; 2,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-15,0; 8,24</t>
+          <t>-14,48; 7,8</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-58,32; -20,48</t>
+          <t>-39,92; -21,87</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-12,29</t>
+          <t>-12,73</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-13,83</t>
+          <t>-12,58</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-13,12</t>
+          <t>-12,65</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 5,88</t>
+          <t>-3,46; 5,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-9,23; 0,14</t>
+          <t>-8,94; 0,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-16,08; -7,95</t>
+          <t>-16,96; -8,3</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,7; 3,97</t>
+          <t>-5,01; 3,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-10,32; -1,87</t>
+          <t>-10,46; -1,51</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-18,45; -10,07</t>
+          <t>-16,02; -8,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 3,5</t>
+          <t>-2,72; 3,33</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,43; -2,34</t>
+          <t>-8,23; -2,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-15,8; -9,98</t>
+          <t>-15,1; -9,71</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-43,96%</t>
+          <t>-45,5%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-48,33%</t>
+          <t>-43,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-46,35%</t>
+          <t>-44,68%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-11,25; 23,21</t>
+          <t>-11,72; 23,17</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-30,16; 0,59</t>
+          <t>-29,48; -0,0</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-54,25; -30,91</t>
+          <t>-55,43; -32,53</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-15,22; 15,11</t>
+          <t>-16,2; 13,65</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-33,9; -7,01</t>
+          <t>-34,59; -5,92</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-59,7; -38,34</t>
+          <t>-52,07; -33,63</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 12,99</t>
+          <t>-9,02; 12,58</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-28,63; -8,86</t>
+          <t>-27,84; -8,49</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-53,29; -37,74</t>
+          <t>-50,95; -36,67</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>-14,05</t>
+          <t>-12,87</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>-14,62</t>
+          <t>-13,74</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-14,34</t>
+          <t>-13,32</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,59; 0,43</t>
+          <t>-4,62; 0,66</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-6,92; -1,84</t>
+          <t>-7,29; -1,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-18,41; -11,35</t>
+          <t>-15,4; -10,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-5,43; -0,57</t>
+          <t>-5,67; -0,78</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,11; -3,24</t>
+          <t>-8,22; -3,13</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-18,25; -11,76</t>
+          <t>-15,78; -11,66</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,53; -0,98</t>
+          <t>-4,29; -0,76</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-6,89; -3,27</t>
+          <t>-7,09; -3,47</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-16,68; -12,24</t>
+          <t>-15,0; -11,61</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>-43,91%</t>
+          <t>-40,24%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>-45,59%</t>
+          <t>-42,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-44,78%</t>
+          <t>-41,6%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-13,73; 1,46</t>
+          <t>-14,0; 2,01</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-20,69; -5,48</t>
+          <t>-21,71; -5,84</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-57,45; -36,86</t>
+          <t>-45,86; -33,43</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-16,3; -1,89</t>
+          <t>-17,05; -2,31</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-24,45; -10,59</t>
+          <t>-24,94; -10,32</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-55,08; -37,47</t>
+          <t>-47,28; -38,05</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-13,74; -3,14</t>
+          <t>-12,87; -2,34</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-20,87; -10,41</t>
+          <t>-21,54; -11,17</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-51,4; -39,13</t>
+          <t>-45,33; -37,14</t>
         </is>
       </c>
     </row>
